--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9AE523-3C2B-43DF-8E9B-F58E57721D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7339CDA5-3CD0-4827-952D-07F3E71E811C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -1790,36 +1790,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AO120"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="16.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.75" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="19.5" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.08984375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.08984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.08984375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.7265625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="19.453125" style="2" customWidth="1"/>
     <col min="16" max="22" width="17" style="2" customWidth="1"/>
-    <col min="23" max="24" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.25" style="2" customWidth="1"/>
-    <col min="29" max="29" width="10.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.125" style="2" customWidth="1"/>
-    <col min="31" max="33" width="71.875" style="2" customWidth="1"/>
-    <col min="34" max="34" width="21.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="37.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="37.875" style="2" customWidth="1"/>
-    <col min="37" max="37" width="37.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="164.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.26953125" style="2" customWidth="1"/>
+    <col min="29" max="29" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.08984375" style="2" customWidth="1"/>
+    <col min="31" max="33" width="71.90625" style="2" customWidth="1"/>
+    <col min="34" max="34" width="21.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="37.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="37.90625" style="2" customWidth="1"/>
+    <col min="37" max="37" width="37.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="164.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="39" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>2</v>
@@ -1928,7 +1928,7 @@
       <c r="AN1" s="9"/>
       <c r="AO1" s="7"/>
     </row>
-    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1973,7 +1973,7 @@
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
     </row>
-    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -2090,7 +2090,7 @@
       <c r="AN3" s="8"/>
       <c r="AO3" s="8"/>
     </row>
-    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>265</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>267</v>
+        <v>136</v>
       </c>
       <c r="O5" s="2" t="s">
         <v>120</v>
@@ -2283,7 +2283,7 @@
       <c r="AH5" s="4"/>
       <c r="AN5" s="4"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -2317,7 +2317,7 @@
         <v>265</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>267</v>
+        <v>135</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>122</v>
@@ -2361,7 +2361,7 @@
       <c r="AH6" s="4"/>
       <c r="AN6" s="4"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>3</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>265</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>267</v>
+        <v>135</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>121</v>
@@ -2438,7 +2438,7 @@
       <c r="AH7" s="4"/>
       <c r="AN7" s="4"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>119</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>238</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="O8" s="2" t="s">
         <v>119</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AN8" s="4"/>
     </row>
-    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>5</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>238</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>179</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AN9" s="4"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>6</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>238</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>120</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AN10" s="4"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>7</v>
       </c>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="AN11" s="4"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="AN12" s="4"/>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AN13" s="4"/>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AN14" s="4"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="AN15" s="4"/>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AN16" s="4"/>
     </row>
-    <row r="17" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="AN17" s="4"/>
     </row>
-    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AN18" s="4"/>
     </row>
-    <row r="19" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>15</v>
       </c>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="AN19" s="4"/>
     </row>
-    <row r="20" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="AN20" s="4"/>
     </row>
-    <row r="21" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>17</v>
       </c>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="AN21" s="4"/>
     </row>
-    <row r="22" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>18</v>
       </c>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="AN22" s="4"/>
     </row>
-    <row r="23" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AN23" s="4"/>
     </row>
-    <row r="24" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AN24" s="4"/>
     </row>
-    <row r="25" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AN25" s="4"/>
     </row>
-    <row r="26" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AN26" s="4"/>
     </row>
-    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>23</v>
       </c>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="AN27" s="4"/>
     </row>
-    <row r="28" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="AN28" s="4"/>
     </row>
-    <row r="29" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="AN29" s="4"/>
     </row>
-    <row r="30" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AN30" s="4"/>
     </row>
-    <row r="31" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="AN31" s="4"/>
     </row>
-    <row r="32" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AN32" s="4"/>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
         <v>29</v>
       </c>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="AN33" s="4"/>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
         <v>30</v>
       </c>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="AN34" s="4"/>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
         <v>31</v>
       </c>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="AN35" s="4"/>
     </row>
-    <row r="36" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B36" s="4">
         <v>32</v>
       </c>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="AN36" s="4"/>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
         <v>33</v>
       </c>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AN37" s="4"/>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B38" s="4">
         <v>34</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B39" s="4">
         <v>35</v>
       </c>
@@ -5115,7 +5115,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B40" s="4">
         <v>36</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
         <v>37</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B42" s="4">
         <v>38</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
         <v>39</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B44" s="4">
         <v>40</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
         <v>41</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B46" s="4">
         <v>42</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
         <v>43</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B48" s="4">
         <v>44</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="49" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="50" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B50" s="4">
         <v>46</v>
       </c>
@@ -6089,7 +6089,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="51" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -6177,7 +6177,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="52" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B52" s="4">
         <v>48</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="53" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
         <v>49</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="54" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B54" s="4">
         <v>50</v>
       </c>
@@ -6437,7 +6437,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="55" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
         <v>51</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="56" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="57" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
         <v>53</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="58" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B58" s="4">
         <v>54</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
         <v>55</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="60" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -6938,7 +6938,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B61" s="4">
         <v>57</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="62" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="63" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B63" s="4">
         <v>59</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="2:38" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B64" s="4">
         <v>60</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
         <v>61</v>
       </c>
@@ -7385,7 +7385,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B66" s="4">
         <v>62</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B67" s="4">
         <v>63</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B68" s="4">
         <v>64</v>
       </c>
@@ -7649,7 +7649,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -7666,7 +7666,7 @@
       <c r="AF69" s="4"/>
       <c r="AG69" s="4"/>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -7692,7 +7692,7 @@
       <c r="AG70" s="4"/>
       <c r="AN70" s="4"/>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -7715,7 +7715,7 @@
       <c r="AG71" s="4"/>
       <c r="AN71" s="4"/>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -7738,7 +7738,7 @@
       <c r="AG72" s="4"/>
       <c r="AN72" s="4"/>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -7761,7 +7761,7 @@
       <c r="AG73" s="4"/>
       <c r="AN73" s="4"/>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -7784,7 +7784,7 @@
       <c r="AG74" s="4"/>
       <c r="AN74" s="4"/>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -7807,7 +7807,7 @@
       <c r="AG75" s="4"/>
       <c r="AN75" s="4"/>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -7830,7 +7830,7 @@
       <c r="AG76" s="4"/>
       <c r="AN76" s="4"/>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -7853,7 +7853,7 @@
       <c r="AG77" s="4"/>
       <c r="AN77" s="4"/>
     </row>
-    <row r="78" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -7876,7 +7876,7 @@
       <c r="AG78" s="4"/>
       <c r="AN78" s="4"/>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -7899,7 +7899,7 @@
       <c r="AG79" s="4"/>
       <c r="AN79" s="4"/>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -7922,7 +7922,7 @@
       <c r="AG80" s="4"/>
       <c r="AN80" s="4"/>
     </row>
-    <row r="81" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -7945,7 +7945,7 @@
       <c r="AG81" s="4"/>
       <c r="AN81" s="4"/>
     </row>
-    <row r="82" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -7968,7 +7968,7 @@
       <c r="AG82" s="4"/>
       <c r="AN82" s="4"/>
     </row>
-    <row r="83" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -7991,7 +7991,7 @@
       <c r="AG83" s="4"/>
       <c r="AN83" s="4"/>
     </row>
-    <row r="84" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -8014,7 +8014,7 @@
       <c r="AG84" s="4"/>
       <c r="AN84" s="4"/>
     </row>
-    <row r="85" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -8037,7 +8037,7 @@
       <c r="AG85" s="4"/>
       <c r="AN85" s="4"/>
     </row>
-    <row r="86" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -8060,7 +8060,7 @@
       <c r="AG86" s="4"/>
       <c r="AN86" s="4"/>
     </row>
-    <row r="87" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -8083,7 +8083,7 @@
       <c r="AG87" s="4"/>
       <c r="AN87" s="4"/>
     </row>
-    <row r="88" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -8106,7 +8106,7 @@
       <c r="AG88" s="4"/>
       <c r="AN88" s="4"/>
     </row>
-    <row r="89" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -8129,7 +8129,7 @@
       <c r="AG89" s="4"/>
       <c r="AN89" s="4"/>
     </row>
-    <row r="90" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -8152,7 +8152,7 @@
       <c r="AG90" s="4"/>
       <c r="AN90" s="4"/>
     </row>
-    <row r="91" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -8175,7 +8175,7 @@
       <c r="AG91" s="4"/>
       <c r="AN91" s="4"/>
     </row>
-    <row r="92" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -8198,7 +8198,7 @@
       <c r="AG92" s="4"/>
       <c r="AN92" s="4"/>
     </row>
-    <row r="93" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:40" x14ac:dyDescent="0.25">
       <c r="B93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -8212,7 +8212,7 @@
       <c r="AG93" s="4"/>
       <c r="AN93" s="4"/>
     </row>
-    <row r="94" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:40" x14ac:dyDescent="0.25">
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="P94" s="6"/>
@@ -8232,7 +8232,7 @@
       <c r="AG94" s="4"/>
       <c r="AN94" s="4"/>
     </row>
-    <row r="95" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:40" x14ac:dyDescent="0.25">
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="P95" s="6"/>
@@ -8252,7 +8252,7 @@
       <c r="AG95" s="4"/>
       <c r="AN95" s="4"/>
     </row>
-    <row r="96" spans="2:40" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:40" x14ac:dyDescent="0.25">
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="P96" s="6"/>
@@ -8272,7 +8272,7 @@
       <c r="AG96" s="4"/>
       <c r="AN96" s="4"/>
     </row>
-    <row r="97" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="97" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="P97" s="6"/>
@@ -8292,7 +8292,7 @@
       <c r="AG97" s="4"/>
       <c r="AN97" s="4"/>
     </row>
-    <row r="98" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="98" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="P98" s="6"/>
@@ -8312,7 +8312,7 @@
       <c r="AG98" s="4"/>
       <c r="AN98" s="4"/>
     </row>
-    <row r="99" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="99" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="P99" s="6"/>
@@ -8332,7 +8332,7 @@
       <c r="AG99" s="4"/>
       <c r="AN99" s="4"/>
     </row>
-    <row r="100" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="100" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="P100" s="6"/>
@@ -8352,7 +8352,7 @@
       <c r="AG100" s="4"/>
       <c r="AN100" s="4"/>
     </row>
-    <row r="101" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="101" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="P101" s="6"/>
@@ -8372,7 +8372,7 @@
       <c r="AG101" s="4"/>
       <c r="AN101" s="4"/>
     </row>
-    <row r="102" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="102" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="P102" s="6"/>
@@ -8392,7 +8392,7 @@
       <c r="AG102" s="4"/>
       <c r="AN102" s="4"/>
     </row>
-    <row r="103" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="103" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="W103" s="4"/>
@@ -8404,7 +8404,7 @@
       <c r="AF103" s="4"/>
       <c r="AG103" s="4"/>
     </row>
-    <row r="104" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="104" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="W104" s="4"/>
@@ -8416,7 +8416,7 @@
       <c r="AF104" s="4"/>
       <c r="AG104" s="4"/>
     </row>
-    <row r="105" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="105" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="W105" s="4"/>
@@ -8428,7 +8428,7 @@
       <c r="AF105" s="4"/>
       <c r="AG105" s="4"/>
     </row>
-    <row r="106" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="106" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="W106" s="4"/>
@@ -8440,7 +8440,7 @@
       <c r="AF106" s="4"/>
       <c r="AG106" s="4"/>
     </row>
-    <row r="107" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="107" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="W107" s="4"/>
@@ -8452,7 +8452,7 @@
       <c r="AF107" s="4"/>
       <c r="AG107" s="4"/>
     </row>
-    <row r="108" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="108" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="W108" s="4"/>
@@ -8464,7 +8464,7 @@
       <c r="AF108" s="4"/>
       <c r="AG108" s="4"/>
     </row>
-    <row r="109" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="109" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="W109" s="4"/>
@@ -8476,7 +8476,7 @@
       <c r="AF109" s="4"/>
       <c r="AG109" s="4"/>
     </row>
-    <row r="110" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="110" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="W110" s="4"/>
@@ -8488,7 +8488,7 @@
       <c r="AF110" s="4"/>
       <c r="AG110" s="4"/>
     </row>
-    <row r="111" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="111" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="W111" s="4"/>
@@ -8500,7 +8500,7 @@
       <c r="AF111" s="4"/>
       <c r="AG111" s="4"/>
     </row>
-    <row r="112" spans="5:40" x14ac:dyDescent="0.15">
+    <row r="112" spans="5:40" x14ac:dyDescent="0.25">
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="W112" s="4"/>
@@ -8512,7 +8512,7 @@
       <c r="AF112" s="4"/>
       <c r="AG112" s="4"/>
     </row>
-    <row r="113" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="113" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="W113" s="4"/>
@@ -8524,7 +8524,7 @@
       <c r="AF113" s="4"/>
       <c r="AG113" s="4"/>
     </row>
-    <row r="114" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="114" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="W114" s="4"/>
@@ -8536,7 +8536,7 @@
       <c r="AF114" s="4"/>
       <c r="AG114" s="4"/>
     </row>
-    <row r="115" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="115" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="W115" s="4"/>
@@ -8548,7 +8548,7 @@
       <c r="AF115" s="4"/>
       <c r="AG115" s="4"/>
     </row>
-    <row r="116" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="116" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="W116" s="4"/>
@@ -8560,7 +8560,7 @@
       <c r="AF116" s="4"/>
       <c r="AG116" s="4"/>
     </row>
-    <row r="117" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="117" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="W117" s="4"/>
@@ -8572,7 +8572,7 @@
       <c r="AF117" s="4"/>
       <c r="AG117" s="4"/>
     </row>
-    <row r="118" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="118" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="W118" s="4"/>
@@ -8584,7 +8584,7 @@
       <c r="AF118" s="4"/>
       <c r="AG118" s="4"/>
     </row>
-    <row r="119" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="119" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="W119" s="4"/>
@@ -8596,7 +8596,7 @@
       <c r="AF119" s="4"/>
       <c r="AG119" s="4"/>
     </row>
-    <row r="120" spans="5:33" x14ac:dyDescent="0.15">
+    <row r="120" spans="5:33" x14ac:dyDescent="0.25">
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="W120" s="4"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7339CDA5-3CD0-4827-952D-07F3E71E811C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D27F405-31F5-42C9-8109-F77A04A2DD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -366,12 +366,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>市场效果提高1.5倍</t>
-  </si>
-  <si>
-    <t>农场效果提高1.5倍</t>
-  </si>
-  <si>
     <t>外交的所需行动力减半，用于亲善的必要资金也减半。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1287,6 +1281,14 @@
   </si>
   <si>
     <t>周围３区格内己方部队攻击力+10，敌方部队攻击力-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市场效果提高1.5倍,无需紧邻市场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>农场效果提高1.5倍,无需紧邻农场</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1790,36 +1792,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AO120"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="5" width="16.08984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.6328125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.08984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.7265625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="19.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="19.453125" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="19.5" style="2" customWidth="1"/>
     <col min="16" max="22" width="17" style="2" customWidth="1"/>
-    <col min="23" max="24" width="10.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.26953125" style="2" customWidth="1"/>
-    <col min="29" max="29" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16.08984375" style="2" customWidth="1"/>
-    <col min="31" max="33" width="71.90625" style="2" customWidth="1"/>
-    <col min="34" max="34" width="21.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="37.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="37.90625" style="2" customWidth="1"/>
-    <col min="37" max="37" width="37.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="164.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.25" style="2" customWidth="1"/>
+    <col min="29" max="29" width="10.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.125" style="2" customWidth="1"/>
+    <col min="31" max="33" width="71.875" style="2" customWidth="1"/>
+    <col min="34" max="34" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="37.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="37.875" style="2" customWidth="1"/>
+    <col min="37" max="37" width="37.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="164.75" style="2" bestFit="1" customWidth="1"/>
     <col min="39" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>2</v>
@@ -1829,87 +1831,87 @@
       </c>
       <c r="D1" s="9"/>
       <c r="E1" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G1" s="14"/>
       <c r="H1" s="14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>51</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>54</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="W1" s="14" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="X1" s="14" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="Y1" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Z1" s="14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA1" s="14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AB1" s="18" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AC1" s="14" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AD1" s="20" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AE1" s="14" t="s">
         <v>56</v>
       </c>
       <c r="AF1" s="14"/>
       <c r="AG1" s="14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AH1" s="9" t="s">
         <v>53</v>
@@ -1928,7 +1930,7 @@
       <c r="AN1" s="9"/>
       <c r="AO1" s="7"/>
     </row>
-    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1973,7 +1975,7 @@
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
     </row>
-    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -1984,113 +1986,113 @@
         <v>13</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P3" s="8" t="s">
         <v>55</v>
       </c>
       <c r="Q3" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="R3" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="U3" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="V3" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="W3" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="X3" s="8" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Z3" s="8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AA3" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB3" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AC3" s="8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AD3" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AE3" s="8" t="s">
         <v>57</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG3" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AH3" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AI3" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="AJ3" s="13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AK3" s="13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AL3" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AM3" s="8"/>
       <c r="AN3" s="8"/>
       <c r="AO3" s="8"/>
     </row>
-    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2101,10 +2103,10 @@
         <v>5</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F4" s="15" t="s">
         <v>8</v>
@@ -2116,7 +2118,7 @@
         <v>8</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J4" s="15" t="s">
         <v>8</v>
@@ -2134,7 +2136,7 @@
         <v>8</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>6</v>
@@ -2152,16 +2154,16 @@
         <v>8</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>8</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="X4" s="15" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Y4" s="15" t="s">
         <v>8</v>
@@ -2170,10 +2172,10 @@
         <v>6</v>
       </c>
       <c r="AA4" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AC4" s="15" t="s">
         <v>8</v>
@@ -2203,10 +2205,10 @@
         <v>5</v>
       </c>
       <c r="AL4" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B5" s="4">
         <v>1</v>
       </c>
@@ -2224,7 +2226,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -2233,16 +2235,16 @@
         <v>0</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
@@ -2267,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC5" s="4">
         <v>250</v>
@@ -2283,7 +2285,7 @@
       <c r="AH5" s="4"/>
       <c r="AN5" s="4"/>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="4">
         <v>2</v>
@@ -2302,7 +2304,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -2311,16 +2313,16 @@
         <v>0</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
@@ -2345,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC6" s="4">
         <v>100</v>
@@ -2361,12 +2363,12 @@
       <c r="AH6" s="4"/>
       <c r="AN6" s="4"/>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B7" s="4">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
@@ -2379,7 +2381,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -2388,16 +2390,16 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6"/>
@@ -2422,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC7" s="4">
         <v>50</v>
@@ -2431,22 +2433,22 @@
         <v>0</v>
       </c>
       <c r="AE7" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AF7" s="4"/>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
       <c r="AN7" s="4"/>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B8" s="4">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2459,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -2468,16 +2470,16 @@
         <v>1500</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6">
@@ -2500,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC8" s="4">
         <v>0</v>
@@ -2514,28 +2516,28 @@
       <c r="AF8" s="4"/>
       <c r="AG8" s="4"/>
       <c r="AH8" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AI8" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="AK8" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="AJ8" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="AK8" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="AL8" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AN8" s="4"/>
     </row>
-    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2548,7 +2550,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J9" s="4">
         <v>26</v>
@@ -2557,16 +2559,16 @@
         <v>2000</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6">
@@ -2589,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC9" s="4">
         <v>0</v>
@@ -2598,33 +2600,33 @@
         <v>0</v>
       </c>
       <c r="AE9" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AF9" s="4"/>
       <c r="AG9" s="4"/>
       <c r="AH9" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AJ9" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AN9" s="4"/>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B10" s="4">
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -2637,7 +2639,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J10" s="4">
         <v>27</v>
@@ -2646,16 +2648,16 @@
         <v>2500</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6">
@@ -2678,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC10" s="4">
         <v>0</v>
@@ -2692,28 +2694,28 @@
       <c r="AF10" s="4"/>
       <c r="AG10" s="4"/>
       <c r="AH10" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AJ10" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AN10" s="4"/>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B11" s="4">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -2726,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J11" s="4">
         <v>0</v>
@@ -2738,13 +2740,13 @@
         <v>1</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6">
@@ -2767,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC11" s="4">
         <v>0</v>
@@ -2781,20 +2783,20 @@
       <c r="AF11" s="4"/>
       <c r="AG11" s="4"/>
       <c r="AH11" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AI11" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AJ11" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AN11" s="4"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B12" s="4">
         <v>8</v>
       </c>
@@ -2812,7 +2814,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J12" s="4">
         <v>26</v>
@@ -2824,13 +2826,13 @@
         <v>1</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6">
@@ -2853,7 +2855,7 @@
         <v>0</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC12" s="4">
         <v>0</v>
@@ -2867,25 +2869,25 @@
       <c r="AF12" s="4"/>
       <c r="AG12" s="4"/>
       <c r="AH12" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AJ12" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AN12" s="4"/>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B13" s="4">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D13" s="4">
         <v>2</v>
@@ -2898,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J13" s="4">
         <v>0</v>
@@ -2916,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
@@ -2937,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC13" s="4">
         <v>0</v>
@@ -2949,20 +2951,20 @@
       <c r="AF13" s="4"/>
       <c r="AG13" s="4"/>
       <c r="AH13" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AJ13" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AN13" s="4"/>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B14" s="4">
         <v>10</v>
       </c>
@@ -2980,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J14" s="4">
         <v>22</v>
@@ -2998,7 +3000,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -3019,32 +3021,32 @@
         <v>0</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC14" s="4">
         <v>0</v>
       </c>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="AF14" s="4"/>
       <c r="AG14" s="4"/>
       <c r="AH14" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AJ14" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="AN14" s="4"/>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B15" s="4">
         <v>11</v>
       </c>
@@ -3062,7 +3064,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4">
         <v>23</v>
@@ -3074,13 +3076,13 @@
         <v>1</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6">
@@ -3103,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC15" s="4">
         <v>0</v>
@@ -3117,20 +3119,20 @@
       <c r="AF15" s="4"/>
       <c r="AG15" s="4"/>
       <c r="AH15" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AJ15" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AK15" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AN15" s="4"/>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.15">
       <c r="B16" s="4">
         <v>12</v>
       </c>
@@ -3148,7 +3150,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J16" s="4">
         <v>0</v>
@@ -3163,10 +3165,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6">
@@ -3189,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="AB16" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC16" s="4">
         <v>0</v>
@@ -3198,28 +3200,28 @@
         <v>3</v>
       </c>
       <c r="AE16" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AF16" s="4"/>
       <c r="AG16" s="4"/>
       <c r="AH16" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AI16" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="AK16" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="AJ16" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="AK16" s="2" t="s">
-        <v>328</v>
-      </c>
       <c r="AL16" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AN16" s="4"/>
     </row>
-    <row r="17" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B17" s="4">
         <v>13</v>
       </c>
@@ -3237,7 +3239,7 @@
         <v>1</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J17" s="4">
         <v>0</v>
@@ -3252,10 +3254,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6">
@@ -3278,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="AB17" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC17" s="4">
         <v>0</v>
@@ -3292,23 +3294,23 @@
       <c r="AF17" s="4"/>
       <c r="AG17" s="4"/>
       <c r="AH17" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AI17" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="AK17" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="AJ17" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="AK17" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="AL17" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AN17" s="4"/>
     </row>
-    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4">
         <v>14</v>
       </c>
@@ -3326,7 +3328,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J18" s="4">
         <v>22</v>
@@ -3344,7 +3346,7 @@
         <v>1</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="6">
@@ -3367,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="AB18" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC18" s="4">
         <v>0</v>
@@ -3381,25 +3383,25 @@
       <c r="AF18" s="4"/>
       <c r="AG18" s="4"/>
       <c r="AH18" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AI18" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AJ18" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK18" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN18" s="4"/>
     </row>
-    <row r="19" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B19" s="4">
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D19" s="4">
         <v>1</v>
@@ -3412,7 +3414,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J19" s="4">
         <v>0</v>
@@ -3430,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
@@ -3449,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="AB19" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC19" s="4">
         <v>0</v>
@@ -3462,17 +3464,17 @@
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
       <c r="AI19" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AJ19" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK19" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN19" s="4"/>
     </row>
-    <row r="20" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B20" s="4">
         <v>16</v>
       </c>
@@ -3490,7 +3492,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J20" s="4">
         <v>0</v>
@@ -3508,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -3527,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC20" s="4">
         <v>0</v>
@@ -3540,22 +3542,22 @@
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
       <c r="AI20" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AJ20" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AK20" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN20" s="4"/>
     </row>
-    <row r="21" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B21" s="4">
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D21" s="4">
         <v>3</v>
@@ -3568,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J21" s="4">
         <v>0</v>
@@ -3586,7 +3588,7 @@
         <v>1</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="6"/>
@@ -3607,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC21" s="4">
         <v>0</v>
@@ -3619,25 +3621,25 @@
       <c r="AF21" s="4"/>
       <c r="AG21" s="4"/>
       <c r="AH21" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ21" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK21" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN21" s="4"/>
     </row>
-    <row r="22" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B22" s="4">
         <v>18</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D22" s="4">
         <v>3</v>
@@ -3650,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J22" s="4">
         <v>31</v>
@@ -3668,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
@@ -3689,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC22" s="4">
         <v>0</v>
@@ -3701,20 +3703,20 @@
       <c r="AF22" s="4"/>
       <c r="AG22" s="4"/>
       <c r="AH22" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AI22" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ22" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK22" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN22" s="4"/>
     </row>
-    <row r="23" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B23" s="4">
         <v>19</v>
       </c>
@@ -3732,7 +3734,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J23" s="4">
         <v>0</v>
@@ -3750,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
@@ -3771,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="AB23" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC23" s="4">
         <v>0</v>
@@ -3783,20 +3785,20 @@
       <c r="AF23" s="4"/>
       <c r="AG23" s="4"/>
       <c r="AH23" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AI23" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ23" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK23" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN23" s="4"/>
     </row>
-    <row r="24" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B24" s="4">
         <v>20</v>
       </c>
@@ -3814,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J24" s="4">
         <v>31</v>
@@ -3832,7 +3834,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6"/>
@@ -3853,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC24" s="4">
         <v>0</v>
@@ -3865,20 +3867,20 @@
       <c r="AF24" s="4"/>
       <c r="AG24" s="4"/>
       <c r="AH24" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AI24" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ24" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK24" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN24" s="4"/>
     </row>
-    <row r="25" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B25" s="4">
         <v>21</v>
       </c>
@@ -3896,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J25" s="4">
         <v>0</v>
@@ -3914,7 +3916,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P25" s="6"/>
       <c r="Q25" s="6"/>
@@ -3935,7 +3937,7 @@
         <v>0</v>
       </c>
       <c r="AB25" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC25" s="4">
         <v>0</v>
@@ -3947,20 +3949,20 @@
       <c r="AF25" s="4"/>
       <c r="AG25" s="4"/>
       <c r="AH25" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AI25" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ25" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK25" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN25" s="4"/>
     </row>
-    <row r="26" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B26" s="4">
         <v>22</v>
       </c>
@@ -3978,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J26" s="4">
         <v>32</v>
@@ -3996,7 +3998,7 @@
         <v>1</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
@@ -4017,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="AB26" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC26" s="4">
         <v>0</v>
@@ -4029,25 +4031,25 @@
       <c r="AF26" s="4"/>
       <c r="AG26" s="4"/>
       <c r="AH26" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AI26" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ26" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK26" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN26" s="4"/>
     </row>
-    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:40" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4">
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D27" s="4">
         <v>3</v>
@@ -4060,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J27" s="4">
         <v>32</v>
@@ -4078,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="6"/>
@@ -4099,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="AB27" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC27" s="4">
         <v>0</v>
@@ -4111,20 +4113,20 @@
       <c r="AF27" s="4"/>
       <c r="AG27" s="4"/>
       <c r="AH27" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AI27" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ27" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK27" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN27" s="4"/>
     </row>
-    <row r="28" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B28" s="4">
         <v>24</v>
       </c>
@@ -4142,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J28" s="4">
         <v>0</v>
@@ -4160,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
@@ -4179,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AB28" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC28" s="4">
         <v>0</v>
@@ -4192,17 +4194,17 @@
       <c r="AG28" s="4"/>
       <c r="AH28" s="4"/>
       <c r="AI28" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ28" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK28" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN28" s="4"/>
     </row>
-    <row r="29" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B29" s="4">
         <v>25</v>
       </c>
@@ -4220,7 +4222,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J29" s="4">
         <v>0</v>
@@ -4238,7 +4240,7 @@
         <v>1</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
@@ -4257,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="AB29" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC29" s="4">
         <v>0</v>
@@ -4270,17 +4272,17 @@
       <c r="AG29" s="4"/>
       <c r="AH29" s="4"/>
       <c r="AI29" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ29" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK29" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN29" s="4"/>
     </row>
-    <row r="30" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B30" s="4">
         <v>26</v>
       </c>
@@ -4298,7 +4300,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J30" s="4">
         <v>0</v>
@@ -4314,7 +4316,7 @@
         <v>1</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
@@ -4333,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="AB30" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC30" s="4">
         <v>0</v>
@@ -4346,17 +4348,17 @@
       <c r="AG30" s="4"/>
       <c r="AH30" s="4"/>
       <c r="AI30" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ30" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK30" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN30" s="4"/>
     </row>
-    <row r="31" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B31" s="4">
         <v>27</v>
       </c>
@@ -4374,7 +4376,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J31" s="4">
         <v>0</v>
@@ -4392,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P31" s="6"/>
       <c r="Q31" s="6"/>
@@ -4411,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="AB31" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC31" s="4">
         <v>0</v>
@@ -4424,17 +4426,17 @@
       <c r="AG31" s="4"/>
       <c r="AH31" s="4"/>
       <c r="AI31" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ31" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK31" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN31" s="4"/>
     </row>
-    <row r="32" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B32" s="4">
         <v>28</v>
       </c>
@@ -4452,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J32" s="4">
         <v>0</v>
@@ -4468,7 +4470,7 @@
         <v>1</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
@@ -4487,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AB32" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AC32" s="4">
         <v>0</v>
@@ -4500,17 +4502,17 @@
       <c r="AG32" s="4"/>
       <c r="AH32" s="4"/>
       <c r="AI32" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ32" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK32" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN32" s="4"/>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B33" s="4">
         <v>29</v>
       </c>
@@ -4528,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J33" s="4">
         <v>0</v>
@@ -4546,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P33" s="6"/>
       <c r="Q33" s="6"/>
@@ -4565,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="AB33" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC33" s="4">
         <v>0</v>
@@ -4578,17 +4580,17 @@
       <c r="AG33" s="4"/>
       <c r="AH33" s="4"/>
       <c r="AI33" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ33" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK33" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN33" s="4"/>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B34" s="4">
         <v>30</v>
       </c>
@@ -4606,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J34" s="4">
         <v>0</v>
@@ -4624,7 +4626,7 @@
         <v>1</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
@@ -4643,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="AB34" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC34" s="4">
         <v>0</v>
@@ -4656,17 +4658,17 @@
       <c r="AG34" s="4"/>
       <c r="AH34" s="4"/>
       <c r="AI34" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ34" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK34" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN34" s="4"/>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B35" s="4">
         <v>31</v>
       </c>
@@ -4684,7 +4686,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J35" s="4">
         <v>0</v>
@@ -4702,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
@@ -4723,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="AB35" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC35" s="4">
         <v>100</v>
@@ -4734,28 +4736,28 @@
       </c>
       <c r="AF35" s="4"/>
       <c r="AG35" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AH35" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AI35" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="AJ35" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AK35" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="AN35" s="4"/>
     </row>
-    <row r="36" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B36" s="4">
         <v>32</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D36" s="4">
         <v>4</v>
@@ -4770,7 +4772,7 @@
         <v>1</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J36" s="4">
         <v>0</v>
@@ -4788,7 +4790,7 @@
         <v>1</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P36" s="6"/>
       <c r="Q36" s="6">
@@ -4813,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="AB36" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC36" s="4">
         <v>30</v>
@@ -4826,28 +4828,28 @@
       </c>
       <c r="AF36" s="4"/>
       <c r="AG36" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="AH36" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="AI36" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="AH36" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="AI36" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="AJ36" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AK36" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AN36" s="4"/>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B37" s="4">
         <v>33</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D37" s="4">
         <v>4</v>
@@ -4862,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J37" s="4">
         <v>0</v>
@@ -4880,7 +4882,7 @@
         <v>1</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P37" s="6"/>
       <c r="Q37" s="6">
@@ -4905,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="AB37" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC37" s="4">
         <v>30</v>
@@ -4918,28 +4920,28 @@
       </c>
       <c r="AF37" s="4"/>
       <c r="AG37" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AH37" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AI37" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AJ37" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AK37" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AN37" s="4"/>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B38" s="4">
         <v>34</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D38" s="4">
         <v>4</v>
@@ -4948,13 +4950,13 @@
         <v>34</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H38" s="4">
         <v>1</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J38" s="4">
         <v>0</v>
@@ -4972,19 +4974,19 @@
         <v>0</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="T38" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="V38" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
@@ -4995,7 +4997,7 @@
         <v>0</v>
       </c>
       <c r="AB38" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC38" s="4">
         <v>30</v>
@@ -5008,27 +5010,27 @@
       </c>
       <c r="AF38" s="4"/>
       <c r="AG38" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AH38" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AI38" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AJ38" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK38" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B39" s="4">
         <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D39" s="4">
         <v>4</v>
@@ -5037,13 +5039,13 @@
         <v>35</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H39" s="4">
         <v>1</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J39" s="4">
         <v>0</v>
@@ -5061,22 +5063,22 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="T39" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="V39" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
@@ -5087,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="AB39" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC39" s="4">
         <v>30</v>
@@ -5100,27 +5102,27 @@
       </c>
       <c r="AF39" s="4"/>
       <c r="AG39" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AH39" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AJ39" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK39" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B40" s="4">
         <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D40" s="4">
         <v>4</v>
@@ -5129,13 +5131,13 @@
         <v>36</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H40" s="4">
         <v>1</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J40" s="4">
         <v>0</v>
@@ -5153,22 +5155,22 @@
         <v>0</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="T40" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="U40" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="V40" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
@@ -5179,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC40" s="4">
         <v>30</v>
@@ -5192,27 +5194,27 @@
       </c>
       <c r="AF40" s="4"/>
       <c r="AG40" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AH40" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AI40" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AJ40" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK40" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="41" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B41" s="4">
         <v>37</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D41" s="4">
         <v>4</v>
@@ -5221,13 +5223,13 @@
         <v>37</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H41" s="4">
         <v>1</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J41" s="4">
         <v>0</v>
@@ -5245,22 +5247,22 @@
         <v>0</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="T41" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="U41" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="V41" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
@@ -5271,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="AB41" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC41" s="4">
         <v>30</v>
@@ -5284,27 +5286,27 @@
       </c>
       <c r="AF41" s="4"/>
       <c r="AG41" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AH41" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI41" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AJ41" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK41" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B42" s="4">
         <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D42" s="4">
         <v>4</v>
@@ -5313,13 +5315,13 @@
         <v>38</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H42" s="4">
         <v>1</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J42" s="4">
         <v>0</v>
@@ -5337,22 +5339,22 @@
         <v>0</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="T42" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="U42" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="V42" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
@@ -5363,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="AB42" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC42" s="4">
         <v>30</v>
@@ -5376,22 +5378,22 @@
       </c>
       <c r="AF42" s="4"/>
       <c r="AG42" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AH42" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AI42" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AJ42" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK42" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B43" s="4">
         <v>39</v>
       </c>
@@ -5408,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J43" s="4">
         <v>0</v>
@@ -5426,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T43" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
@@ -5446,7 +5448,7 @@
         <v>0</v>
       </c>
       <c r="AB43" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC43" s="4">
         <v>30</v>
@@ -5455,36 +5457,36 @@
         <v>3</v>
       </c>
       <c r="AE43" s="4" t="s">
-        <v>91</v>
+        <v>340</v>
       </c>
       <c r="AF43" s="4">
         <v>1</v>
       </c>
       <c r="AG43" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH43" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AI43" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="AJ43" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK43" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AL43" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="44" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B44" s="4">
         <v>40</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D44" s="4">
         <v>4</v>
@@ -5496,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J44" s="4">
         <v>0</v>
@@ -5514,16 +5516,16 @@
         <v>0</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T44" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
@@ -5534,7 +5536,7 @@
         <v>0</v>
       </c>
       <c r="AB44" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC44" s="4">
         <v>30</v>
@@ -5543,31 +5545,31 @@
         <v>3</v>
       </c>
       <c r="AE44" s="4" t="s">
-        <v>92</v>
+        <v>341</v>
       </c>
       <c r="AF44" s="4">
         <v>1</v>
       </c>
       <c r="AG44" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH44" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AI44" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AJ44" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK44" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AL44" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="45" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B45" s="4">
         <v>41</v>
       </c>
@@ -5584,7 +5586,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J45" s="4">
         <v>0</v>
@@ -5602,16 +5604,16 @@
         <v>0</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T45" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
@@ -5622,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="AB45" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC45" s="4">
         <v>30</v>
@@ -5631,33 +5633,33 @@
         <v>2</v>
       </c>
       <c r="AE45" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AF45" s="4">
         <v>1</v>
       </c>
       <c r="AG45" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH45" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AI45" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AJ45" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK45" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B46" s="4">
         <v>42</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D46" s="4">
         <v>4</v>
@@ -5669,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J46" s="4">
         <v>0</v>
@@ -5687,22 +5689,22 @@
         <v>0</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="T46" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="V46" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
@@ -5713,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="AB46" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC46" s="4">
         <v>30</v>
@@ -5722,28 +5724,28 @@
         <v>0</v>
       </c>
       <c r="AE46" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AF46" s="4">
         <v>1</v>
       </c>
       <c r="AG46" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH46" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AI46" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AJ46" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK46" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B47" s="4">
         <v>43</v>
       </c>
@@ -5760,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J47" s="4">
         <v>0</v>
@@ -5778,19 +5780,19 @@
         <v>0</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="T47" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
@@ -5801,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="AB47" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC47" s="4">
         <v>30</v>
@@ -5810,28 +5812,28 @@
         <v>2</v>
       </c>
       <c r="AE47" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AF47" s="4">
         <v>1</v>
       </c>
       <c r="AG47" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH47" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AJ47" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK47" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="48" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B48" s="4">
         <v>44</v>
       </c>
@@ -5848,7 +5850,7 @@
         <v>1</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J48" s="4">
         <v>0</v>
@@ -5866,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T48" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
@@ -5886,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="AB48" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC48" s="4">
         <v>30</v>
@@ -5895,28 +5897,28 @@
         <v>3</v>
       </c>
       <c r="AE48" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AF48" s="4">
         <v>1</v>
       </c>
       <c r="AG48" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH48" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AI48" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AJ48" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK48" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="49" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B49" s="4">
         <v>45</v>
       </c>
@@ -5933,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J49" s="4">
         <v>0</v>
@@ -5951,16 +5953,16 @@
         <v>0</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
@@ -5971,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="AB49" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC49" s="4">
         <v>30</v>
@@ -5980,33 +5982,33 @@
         <v>2</v>
       </c>
       <c r="AE49" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AF49" s="4">
         <v>1</v>
       </c>
       <c r="AG49" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH49" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AI49" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AJ49" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK49" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="50" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="50" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B50" s="4">
         <v>46</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D50" s="4">
         <v>4</v>
@@ -6018,7 +6020,7 @@
         <v>1</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J50" s="4">
         <v>0</v>
@@ -6036,19 +6038,19 @@
         <v>0</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="T50" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
@@ -6059,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="AB50" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC50" s="4">
         <v>30</v>
@@ -6068,28 +6070,28 @@
         <v>0</v>
       </c>
       <c r="AE50" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AF50" s="4">
         <v>1</v>
       </c>
       <c r="AG50" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH50" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AI50" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AJ50" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK50" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="51" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="51" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B51" s="4">
         <v>47</v>
       </c>
@@ -6106,7 +6108,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J51" s="4">
         <v>0</v>
@@ -6124,17 +6126,17 @@
         <v>0</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S51" s="4"/>
       <c r="T51" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W51" s="4">
         <v>240</v>
@@ -6147,7 +6149,7 @@
         <v>0</v>
       </c>
       <c r="AB51" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC51" s="4">
         <v>30</v>
@@ -6156,28 +6158,28 @@
         <v>3</v>
       </c>
       <c r="AE51" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AF51" s="4">
         <v>3</v>
       </c>
       <c r="AG51" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AH51" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AI51" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AJ51" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK51" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="52" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="52" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B52" s="4">
         <v>48</v>
       </c>
@@ -6194,7 +6196,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J52" s="4">
         <v>0</v>
@@ -6212,17 +6214,17 @@
         <v>0</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S52" s="4"/>
       <c r="T52" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W52" s="4">
         <v>180</v>
@@ -6235,7 +6237,7 @@
         <v>0</v>
       </c>
       <c r="AB52" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC52" s="4">
         <v>30</v>
@@ -6244,28 +6246,28 @@
         <v>3</v>
       </c>
       <c r="AE52" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AF52" s="4">
         <v>2</v>
       </c>
       <c r="AG52" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AH52" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AI52" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="AJ52" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK52" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="53" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B53" s="4">
         <v>49</v>
       </c>
@@ -6282,7 +6284,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J53" s="4">
         <v>0</v>
@@ -6300,14 +6302,14 @@
         <v>0</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S53" s="4"/>
       <c r="T53" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W53" s="4">
         <v>60</v>
@@ -6320,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="AB53" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC53" s="4">
         <v>0</v>
@@ -6329,24 +6331,24 @@
         <v>3</v>
       </c>
       <c r="AE53" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AF53" s="4"/>
       <c r="AG53" s="4"/>
       <c r="AH53" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AI53" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AJ53" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK53" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="54" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="54" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B54" s="4">
         <v>50</v>
       </c>
@@ -6363,7 +6365,7 @@
         <v>1</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J54" s="4">
         <v>0</v>
@@ -6381,17 +6383,17 @@
         <v>0</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S54" s="4"/>
       <c r="T54" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W54" s="4"/>
       <c r="X54" s="4">
@@ -6404,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="AB54" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC54" s="4">
         <v>30</v>
@@ -6413,31 +6415,31 @@
         <v>0</v>
       </c>
       <c r="AE54" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AF54" s="4">
         <v>1</v>
       </c>
       <c r="AG54" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AH54" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="AI54" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AJ54" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK54" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AL54" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="55" spans="2:38" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B55" s="4">
         <v>51</v>
       </c>
@@ -6451,13 +6453,13 @@
         <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H55" s="4">
         <v>2</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J55" s="4">
         <v>0</v>
@@ -6475,14 +6477,14 @@
         <v>0</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S55" s="4"/>
       <c r="T55" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W55" s="4">
         <v>90</v>
@@ -6495,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="AB55" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC55" s="4">
         <v>20</v>
@@ -6504,24 +6506,24 @@
         <v>3</v>
       </c>
       <c r="AE55" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF55" s="4"/>
       <c r="AG55" s="4"/>
       <c r="AH55" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AI55" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AJ55" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK55" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="56" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B56" s="4">
         <v>52</v>
       </c>
@@ -6538,7 +6540,7 @@
         <v>3</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J56" s="4">
         <v>0</v>
@@ -6556,14 +6558,14 @@
         <v>0</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S56" s="4"/>
       <c r="T56" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="W56" s="4">
         <v>120</v>
@@ -6576,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="AB56" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC56" s="4">
         <v>20</v>
@@ -6585,24 +6587,24 @@
         <v>3</v>
       </c>
       <c r="AE56" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF56" s="4"/>
       <c r="AG56" s="4"/>
       <c r="AH56" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AJ56" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK56" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="57" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="57" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B57" s="4">
         <v>53</v>
       </c>
@@ -6616,13 +6618,13 @@
         <v>33</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H57" s="4">
         <v>2</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J57" s="4">
         <v>0</v>
@@ -6640,14 +6642,14 @@
         <v>0</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S57" s="4"/>
       <c r="T57" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W57" s="4"/>
       <c r="X57" s="4">
@@ -6660,7 +6662,7 @@
         <v>0</v>
       </c>
       <c r="AB57" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC57" s="4">
         <v>20</v>
@@ -6669,24 +6671,24 @@
         <v>3</v>
       </c>
       <c r="AE57" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF57" s="4"/>
       <c r="AG57" s="4"/>
       <c r="AH57" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AI57" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AJ57" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK57" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="58" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B58" s="4">
         <v>54</v>
       </c>
@@ -6703,7 +6705,7 @@
         <v>3</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J58" s="4">
         <v>0</v>
@@ -6721,14 +6723,14 @@
         <v>0</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S58" s="4"/>
       <c r="T58" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="W58" s="4"/>
       <c r="X58" s="4">
@@ -6741,7 +6743,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC58" s="4">
         <v>20</v>
@@ -6750,24 +6752,24 @@
         <v>3</v>
       </c>
       <c r="AE58" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF58" s="4"/>
       <c r="AG58" s="4"/>
       <c r="AH58" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AI58" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AJ58" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK58" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="59" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B59" s="4">
         <v>55</v>
       </c>
@@ -6781,13 +6783,13 @@
         <v>34</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H59" s="4">
         <v>2</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J59" s="4">
         <v>0</v>
@@ -6805,19 +6807,19 @@
         <v>0</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="T59" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
@@ -6828,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="AB59" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC59" s="4">
         <v>20</v>
@@ -6837,24 +6839,24 @@
         <v>4</v>
       </c>
       <c r="AE59" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF59" s="4"/>
       <c r="AG59" s="4"/>
       <c r="AH59" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AI59" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AJ59" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK59" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="60" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="60" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B60" s="4">
         <v>56</v>
       </c>
@@ -6871,7 +6873,7 @@
         <v>3</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J60" s="4">
         <v>0</v>
@@ -6889,19 +6891,19 @@
         <v>0</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="T60" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
@@ -6912,7 +6914,7 @@
         <v>0</v>
       </c>
       <c r="AB60" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC60" s="4">
         <v>20</v>
@@ -6921,24 +6923,24 @@
         <v>4</v>
       </c>
       <c r="AE60" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF60" s="4"/>
       <c r="AG60" s="4"/>
       <c r="AH60" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AI60" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AJ60" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK60" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="61" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="61" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B61" s="4">
         <v>57</v>
       </c>
@@ -6952,13 +6954,13 @@
         <v>35</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H61" s="4">
         <v>2</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J61" s="4">
         <v>0</v>
@@ -6976,22 +6978,22 @@
         <v>0</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="U61" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
@@ -7002,7 +7004,7 @@
         <v>0</v>
       </c>
       <c r="AB61" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC61" s="4">
         <v>20</v>
@@ -7011,24 +7013,24 @@
         <v>2</v>
       </c>
       <c r="AE61" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF61" s="4"/>
       <c r="AG61" s="4"/>
       <c r="AH61" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AI61" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="AJ61" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="AJ61" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="AK61" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="62" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="62" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B62" s="4">
         <v>58</v>
       </c>
@@ -7045,7 +7047,7 @@
         <v>3</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J62" s="4">
         <v>0</v>
@@ -7063,22 +7065,22 @@
         <v>0</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="U62" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="V62" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
@@ -7089,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="AB62" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC62" s="4">
         <v>20</v>
@@ -7098,24 +7100,24 @@
         <v>2</v>
       </c>
       <c r="AE62" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF62" s="4"/>
       <c r="AG62" s="4"/>
       <c r="AH62" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AI62" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="AJ62" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="AJ62" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="AK62" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="63" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="63" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B63" s="4">
         <v>59</v>
       </c>
@@ -7135,7 +7137,7 @@
         <v>2</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J63" s="4">
         <v>0</v>
@@ -7153,22 +7155,22 @@
         <v>0</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="U63" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="V63" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
@@ -7180,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="AB63" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC63" s="4">
         <v>20</v>
@@ -7189,24 +7191,24 @@
         <v>2</v>
       </c>
       <c r="AE63" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF63" s="4"/>
       <c r="AG63" s="4"/>
       <c r="AH63" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AI63" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AJ63" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK63" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="64" spans="2:38" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="64" spans="2:38" x14ac:dyDescent="0.15">
       <c r="B64" s="4">
         <v>60</v>
       </c>
@@ -7224,7 +7226,7 @@
         <v>3</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J64" s="4">
         <v>0</v>
@@ -7242,22 +7244,22 @@
         <v>0</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="U64" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="V64" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
@@ -7269,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="AB64" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC64" s="4">
         <v>20</v>
@@ -7278,29 +7280,29 @@
         <v>2</v>
       </c>
       <c r="AE64" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AF64" s="4"/>
       <c r="AG64" s="4"/>
       <c r="AH64" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AI64" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AJ64" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK64" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B65" s="4">
         <v>61</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D65" s="4">
         <v>4</v>
@@ -7309,13 +7311,13 @@
         <v>37</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H65" s="4">
         <v>2</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J65" s="4">
         <v>0</v>
@@ -7333,22 +7335,22 @@
         <v>0</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="V65" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
@@ -7359,7 +7361,7 @@
         <v>0</v>
       </c>
       <c r="AB65" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC65" s="4">
         <v>30</v>
@@ -7373,24 +7375,24 @@
       <c r="AF65" s="4"/>
       <c r="AG65" s="4"/>
       <c r="AH65" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI65" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AJ65" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK65" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="66" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B66" s="4">
         <v>62</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D66" s="4">
         <v>4</v>
@@ -7402,7 +7404,7 @@
         <v>3</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J66" s="4">
         <v>0</v>
@@ -7420,22 +7422,22 @@
         <v>0</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="T66" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="V66" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
@@ -7446,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="AB66" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC66" s="4">
         <v>30</v>
@@ -7460,24 +7462,24 @@
       <c r="AF66" s="4"/>
       <c r="AG66" s="4"/>
       <c r="AH66" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI66" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AJ66" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK66" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="67" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B67" s="4">
         <v>63</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D67" s="4">
         <v>4</v>
@@ -7486,13 +7488,13 @@
         <v>38</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H67" s="4">
         <v>2</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J67" s="4">
         <v>0</v>
@@ -7510,22 +7512,22 @@
         <v>0</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="V67" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
@@ -7536,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="AB67" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC67" s="4">
         <v>30</v>
@@ -7550,24 +7552,24 @@
       <c r="AF67" s="4"/>
       <c r="AG67" s="4"/>
       <c r="AH67" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AI67" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AJ67" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK67" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B68" s="4">
         <v>64</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D68" s="4">
         <v>4</v>
@@ -7579,7 +7581,7 @@
         <v>3</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J68" s="4">
         <v>0</v>
@@ -7597,22 +7599,22 @@
         <v>0</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="V68" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
@@ -7623,7 +7625,7 @@
         <v>0</v>
       </c>
       <c r="AB68" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AC68" s="4">
         <v>30</v>
@@ -7637,19 +7639,19 @@
       <c r="AF68" s="4"/>
       <c r="AG68" s="4"/>
       <c r="AH68" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AI68" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AJ68" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AK68" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="69" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -7666,7 +7668,7 @@
       <c r="AF69" s="4"/>
       <c r="AG69" s="4"/>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -7692,7 +7694,7 @@
       <c r="AG70" s="4"/>
       <c r="AN70" s="4"/>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -7715,7 +7717,7 @@
       <c r="AG71" s="4"/>
       <c r="AN71" s="4"/>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -7738,7 +7740,7 @@
       <c r="AG72" s="4"/>
       <c r="AN72" s="4"/>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -7761,7 +7763,7 @@
       <c r="AG73" s="4"/>
       <c r="AN73" s="4"/>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -7784,7 +7786,7 @@
       <c r="AG74" s="4"/>
       <c r="AN74" s="4"/>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -7807,7 +7809,7 @@
       <c r="AG75" s="4"/>
       <c r="AN75" s="4"/>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -7830,7 +7832,7 @@
       <c r="AG76" s="4"/>
       <c r="AN76" s="4"/>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
@@ -7853,7 +7855,7 @@
       <c r="AG77" s="4"/>
       <c r="AN77" s="4"/>
     </row>
-    <row r="78" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -7876,7 +7878,7 @@
       <c r="AG78" s="4"/>
       <c r="AN78" s="4"/>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -7899,7 +7901,7 @@
       <c r="AG79" s="4"/>
       <c r="AN79" s="4"/>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -7922,7 +7924,7 @@
       <c r="AG80" s="4"/>
       <c r="AN80" s="4"/>
     </row>
-    <row r="81" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -7945,7 +7947,7 @@
       <c r="AG81" s="4"/>
       <c r="AN81" s="4"/>
     </row>
-    <row r="82" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -7968,7 +7970,7 @@
       <c r="AG82" s="4"/>
       <c r="AN82" s="4"/>
     </row>
-    <row r="83" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -7991,7 +7993,7 @@
       <c r="AG83" s="4"/>
       <c r="AN83" s="4"/>
     </row>
-    <row r="84" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -8014,7 +8016,7 @@
       <c r="AG84" s="4"/>
       <c r="AN84" s="4"/>
     </row>
-    <row r="85" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -8037,7 +8039,7 @@
       <c r="AG85" s="4"/>
       <c r="AN85" s="4"/>
     </row>
-    <row r="86" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -8060,7 +8062,7 @@
       <c r="AG86" s="4"/>
       <c r="AN86" s="4"/>
     </row>
-    <row r="87" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -8083,7 +8085,7 @@
       <c r="AG87" s="4"/>
       <c r="AN87" s="4"/>
     </row>
-    <row r="88" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -8106,7 +8108,7 @@
       <c r="AG88" s="4"/>
       <c r="AN88" s="4"/>
     </row>
-    <row r="89" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -8129,7 +8131,7 @@
       <c r="AG89" s="4"/>
       <c r="AN89" s="4"/>
     </row>
-    <row r="90" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -8152,7 +8154,7 @@
       <c r="AG90" s="4"/>
       <c r="AN90" s="4"/>
     </row>
-    <row r="91" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -8175,7 +8177,7 @@
       <c r="AG91" s="4"/>
       <c r="AN91" s="4"/>
     </row>
-    <row r="92" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -8198,7 +8200,7 @@
       <c r="AG92" s="4"/>
       <c r="AN92" s="4"/>
     </row>
-    <row r="93" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -8212,7 +8214,7 @@
       <c r="AG93" s="4"/>
       <c r="AN93" s="4"/>
     </row>
-    <row r="94" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="P94" s="6"/>
@@ -8232,7 +8234,7 @@
       <c r="AG94" s="4"/>
       <c r="AN94" s="4"/>
     </row>
-    <row r="95" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="P95" s="6"/>
@@ -8252,7 +8254,7 @@
       <c r="AG95" s="4"/>
       <c r="AN95" s="4"/>
     </row>
-    <row r="96" spans="2:40" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:40" x14ac:dyDescent="0.15">
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="P96" s="6"/>
@@ -8272,7 +8274,7 @@
       <c r="AG96" s="4"/>
       <c r="AN96" s="4"/>
     </row>
-    <row r="97" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="P97" s="6"/>
@@ -8292,7 +8294,7 @@
       <c r="AG97" s="4"/>
       <c r="AN97" s="4"/>
     </row>
-    <row r="98" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="P98" s="6"/>
@@ -8312,7 +8314,7 @@
       <c r="AG98" s="4"/>
       <c r="AN98" s="4"/>
     </row>
-    <row r="99" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="P99" s="6"/>
@@ -8332,7 +8334,7 @@
       <c r="AG99" s="4"/>
       <c r="AN99" s="4"/>
     </row>
-    <row r="100" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="P100" s="6"/>
@@ -8352,7 +8354,7 @@
       <c r="AG100" s="4"/>
       <c r="AN100" s="4"/>
     </row>
-    <row r="101" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="P101" s="6"/>
@@ -8372,7 +8374,7 @@
       <c r="AG101" s="4"/>
       <c r="AN101" s="4"/>
     </row>
-    <row r="102" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="P102" s="6"/>
@@ -8392,7 +8394,7 @@
       <c r="AG102" s="4"/>
       <c r="AN102" s="4"/>
     </row>
-    <row r="103" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="W103" s="4"/>
@@ -8404,7 +8406,7 @@
       <c r="AF103" s="4"/>
       <c r="AG103" s="4"/>
     </row>
-    <row r="104" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="W104" s="4"/>
@@ -8416,7 +8418,7 @@
       <c r="AF104" s="4"/>
       <c r="AG104" s="4"/>
     </row>
-    <row r="105" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="W105" s="4"/>
@@ -8428,7 +8430,7 @@
       <c r="AF105" s="4"/>
       <c r="AG105" s="4"/>
     </row>
-    <row r="106" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="W106" s="4"/>
@@ -8440,7 +8442,7 @@
       <c r="AF106" s="4"/>
       <c r="AG106" s="4"/>
     </row>
-    <row r="107" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="107" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="W107" s="4"/>
@@ -8452,7 +8454,7 @@
       <c r="AF107" s="4"/>
       <c r="AG107" s="4"/>
     </row>
-    <row r="108" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="108" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="W108" s="4"/>
@@ -8464,7 +8466,7 @@
       <c r="AF108" s="4"/>
       <c r="AG108" s="4"/>
     </row>
-    <row r="109" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="109" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="W109" s="4"/>
@@ -8476,7 +8478,7 @@
       <c r="AF109" s="4"/>
       <c r="AG109" s="4"/>
     </row>
-    <row r="110" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="W110" s="4"/>
@@ -8488,7 +8490,7 @@
       <c r="AF110" s="4"/>
       <c r="AG110" s="4"/>
     </row>
-    <row r="111" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="W111" s="4"/>
@@ -8500,7 +8502,7 @@
       <c r="AF111" s="4"/>
       <c r="AG111" s="4"/>
     </row>
-    <row r="112" spans="5:40" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:40" x14ac:dyDescent="0.15">
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="W112" s="4"/>
@@ -8512,7 +8514,7 @@
       <c r="AF112" s="4"/>
       <c r="AG112" s="4"/>
     </row>
-    <row r="113" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="W113" s="4"/>
@@ -8524,7 +8526,7 @@
       <c r="AF113" s="4"/>
       <c r="AG113" s="4"/>
     </row>
-    <row r="114" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="W114" s="4"/>
@@ -8536,7 +8538,7 @@
       <c r="AF114" s="4"/>
       <c r="AG114" s="4"/>
     </row>
-    <row r="115" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="W115" s="4"/>
@@ -8548,7 +8550,7 @@
       <c r="AF115" s="4"/>
       <c r="AG115" s="4"/>
     </row>
-    <row r="116" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="W116" s="4"/>
@@ -8560,7 +8562,7 @@
       <c r="AF116" s="4"/>
       <c r="AG116" s="4"/>
     </row>
-    <row r="117" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="W117" s="4"/>
@@ -8572,7 +8574,7 @@
       <c r="AF117" s="4"/>
       <c r="AG117" s="4"/>
     </row>
-    <row r="118" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="W118" s="4"/>
@@ -8584,7 +8586,7 @@
       <c r="AF118" s="4"/>
       <c r="AG118" s="4"/>
     </row>
-    <row r="119" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="W119" s="4"/>
@@ -8596,7 +8598,7 @@
       <c r="AF119" s="4"/>
       <c r="AG119" s="4"/>
     </row>
-    <row r="120" spans="5:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:33" x14ac:dyDescent="0.15">
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="W120" s="4"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D27F405-31F5-42C9-8109-F77A04A2DD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3594621-0455-4CB9-A5FE-B2A1398F3097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BuildingTypes" sheetId="36" r:id="rId1"/>
@@ -5439,7 +5439,9 @@
       <c r="T43" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="W43" s="4"/>
+      <c r="W43" s="4">
+        <v>1</v>
+      </c>
       <c r="X43" s="4"/>
       <c r="Z43" s="4">
         <v>400</v>
@@ -5528,7 +5530,9 @@
         <v>117</v>
       </c>
       <c r="W44" s="4"/>
-      <c r="X44" s="4"/>
+      <c r="X44" s="4">
+        <v>1</v>
+      </c>
       <c r="Z44" s="4">
         <v>400</v>
       </c>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3594621-0455-4CB9-A5FE-B2A1398F3097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EDF524-C4B1-429E-BC70-BE5A18E67B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="343">
   <si>
     <t>0</t>
   </si>
@@ -1289,6 +1289,10 @@
   </si>
   <si>
     <t>农场效果提高1.5倍,无需紧邻农场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>都市(小)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7656,21 +7660,81 @@
       </c>
     </row>
     <row r="69" spans="2:40" x14ac:dyDescent="0.15">
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
-      <c r="AC69" s="4"/>
-      <c r="AD69" s="4"/>
-      <c r="AE69" s="4"/>
+      <c r="B69" s="4">
+        <v>65</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="D69" s="4">
+        <v>0</v>
+      </c>
+      <c r="E69" s="4">
+        <v>5</v>
+      </c>
+      <c r="F69" s="4"/>
+      <c r="H69" s="4">
+        <v>1</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J69" s="4">
+        <v>0</v>
+      </c>
+      <c r="K69" s="4">
+        <v>0</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="6"/>
+      <c r="R69" s="6"/>
+      <c r="S69" s="6"/>
+      <c r="T69" s="6">
+        <v>21</v>
+      </c>
+      <c r="U69" s="6"/>
+      <c r="V69" s="6"/>
+      <c r="W69" s="4">
+        <v>600</v>
+      </c>
+      <c r="X69" s="4">
+        <v>5600</v>
+      </c>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC69" s="4">
+        <v>250</v>
+      </c>
+      <c r="AD69" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="AF69" s="4"/>
       <c r="AG69" s="4"/>
+      <c r="AH69" s="4"/>
+      <c r="AN69" s="4"/>
     </row>
     <row r="70" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B70" s="4"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EDF524-C4B1-429E-BC70-BE5A18E67B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D178D64F-2A7C-45B5-9DC2-A8354DFCBD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="344">
   <si>
     <t>0</t>
   </si>
@@ -1293,6 +1293,10 @@
   </si>
   <si>
     <t>都市(小)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,4,13</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5079,7 +5083,7 @@
         <v>261</v>
       </c>
       <c r="U39" s="2" t="s">
-        <v>235</v>
+        <v>343</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>246</v>
@@ -7741,18 +7745,10 @@
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
       <c r="J70" s="4"/>
-      <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-      <c r="U70" s="6"/>
-      <c r="V70" s="6"/>
+      <c r="K70" s="4"/>
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
-      <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
       <c r="AA70" s="4"/>
       <c r="AC70" s="4"/>
@@ -7760,7 +7756,6 @@
       <c r="AE70" s="4"/>
       <c r="AF70" s="4"/>
       <c r="AG70" s="4"/>
-      <c r="AN70" s="4"/>
     </row>
     <row r="71" spans="2:40" x14ac:dyDescent="0.15">
       <c r="B71" s="4"/>

--- a/Data/Export/Common/BuildingType_建筑类型.xlsx
+++ b/Data/Export/Common/BuildingType_建筑类型.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D178D64F-2A7C-45B5-9DC2-A8354DFCBD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A451876-589C-4EB2-B315-F6E305015D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
